--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Romania Liga I_20242025.xlsx
@@ -68945,19 +68945,19 @@
         <v>8</v>
       </c>
       <c r="AV314" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW314" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX314" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY314" t="n">
         <v>14</v>
       </c>
-      <c r="AX314" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY314" t="n">
-        <v>22</v>
-      </c>
       <c r="AZ314" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA314" t="n">
         <v>8</v>
@@ -69106,16 +69106,16 @@
         <v>2.98</v>
       </c>
       <c r="AC315" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AD315" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AE315" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF315" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG315" t="n">
         <v>1.92</v>
@@ -69130,13 +69130,13 @@
         <v>1.8</v>
       </c>
       <c r="AK315" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL315" t="n">
         <v>0</v>
       </c>
       <c r="AM315" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AN315" t="n">
         <v>1.89</v>
@@ -69160,22 +69160,22 @@
         <v>2.69</v>
       </c>
       <c r="AU315" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV315" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW315" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AX315" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AY315" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AZ315" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA315" t="n">
         <v>9</v>
@@ -69187,43 +69187,43 @@
         <v>13</v>
       </c>
       <c r="BD315" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BE315" t="n">
-        <v>0</v>
+        <v>7.78</v>
       </c>
       <c r="BF315" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BG315" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BH315" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BI315" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BJ315" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BK315" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BL315" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BM315" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="BN315" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BO315" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="BP315" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="316">
@@ -69381,19 +69381,19 @@
         <v>5</v>
       </c>
       <c r="AV316" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW316" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX316" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY316" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ316" t="n">
         <v>4</v>
-      </c>
-      <c r="AW316" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX316" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY316" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ316" t="n">
-        <v>6</v>
       </c>
       <c r="BA316" t="n">
         <v>4</v>
